--- a/44_心理学/50_音乐疗愈/浥尘伙伴社团原创音乐库.xlsx
+++ b/44_心理学/50_音乐疗愈/浥尘伙伴社团原创音乐库.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="0" windowWidth="24500" windowHeight="12800"/>
+    <workbookView xWindow="2200" yWindow="0" windowWidth="24500" windowHeight="12800"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>音乐名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -99,6 +99,26 @@
   </si>
   <si>
     <t>校园</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沧桑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>颓废</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>凌乱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不济</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>逆反</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -429,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:X2"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="4.83203125" bestFit="1" customWidth="1"/>
@@ -439,7 +459,7 @@
     <col min="8" max="19" width="4.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -462,7 +482,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="H2" t="s">
         <v>6</v>
       </c>
@@ -498,6 +518,21 @@
       </c>
       <c r="S2" t="s">
         <v>17</v>
+      </c>
+      <c r="T2" t="s">
+        <v>19</v>
+      </c>
+      <c r="U2" t="s">
+        <v>20</v>
+      </c>
+      <c r="V2" t="s">
+        <v>21</v>
+      </c>
+      <c r="W2" t="s">
+        <v>22</v>
+      </c>
+      <c r="X2" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
